--- a/examples/TAAT/ใบสั่งงาน TAAT.xlsx
+++ b/examples/TAAT/ใบสั่งงาน TAAT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vatska\software\examples\TAAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17C9108-E61C-4C85-A699-1E624C8B9206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43BB9E59-8546-4012-89BB-A00488E44987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{874D8AF1-DF56-4DEE-86B1-A5E2F5D42D71}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="135">
   <si>
     <r>
       <t>บริษัท แวตสก้า จำกัด/ Vatska Company Limited</t>
@@ -487,9 +487,6 @@
   </si>
   <si>
     <t>What if " LMT55, Pharmed or E3603" then show dropdown list" worksheet A2, column D,E,F -line 38-48</t>
-  </si>
-  <si>
-    <t>LMT_55</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1148,58 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1160,61 +1208,10 @@
     <xf numFmtId="164" fontId="15" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1739,7 +1736,7 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>685804</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>324768</xdr:rowOff>
+      <xdr:rowOff>320958</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1781,7 +1778,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>701040</xdr:colOff>
+      <xdr:colOff>704850</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>932</xdr:rowOff>
     </xdr:to>
@@ -1825,9 +1822,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>708133</xdr:colOff>
+      <xdr:colOff>704323</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>286703</xdr:rowOff>
+      <xdr:rowOff>282893</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1869,9 +1866,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>701992</xdr:colOff>
+      <xdr:colOff>705802</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>287839</xdr:rowOff>
+      <xdr:rowOff>284029</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1913,7 +1910,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>704850</xdr:colOff>
+      <xdr:colOff>701040</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>121</xdr:rowOff>
     </xdr:to>
@@ -1957,7 +1954,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>702945</xdr:colOff>
+      <xdr:colOff>706755</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>2086</xdr:rowOff>
     </xdr:to>
@@ -2001,9 +1998,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>705277</xdr:colOff>
+      <xdr:colOff>701467</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>288608</xdr:rowOff>
+      <xdr:rowOff>284798</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2045,7 +2042,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>705802</xdr:colOff>
+      <xdr:colOff>701992</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>2527</xdr:rowOff>
     </xdr:to>
@@ -2091,7 +2088,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>689085</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>284798</xdr:rowOff>
+      <xdr:rowOff>288608</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2133,7 +2130,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>705803</xdr:colOff>
+      <xdr:colOff>701993</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>184</xdr:rowOff>
     </xdr:to>
@@ -2177,9 +2174,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>705276</xdr:colOff>
+      <xdr:colOff>701466</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>283366</xdr:rowOff>
+      <xdr:rowOff>287176</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2221,7 +2218,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>707707</xdr:colOff>
+      <xdr:colOff>703897</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>121</xdr:rowOff>
     </xdr:to>
@@ -2309,7 +2306,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>707707</xdr:colOff>
+      <xdr:colOff>703897</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>304921</xdr:rowOff>
     </xdr:to>
@@ -2353,9 +2350,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>701045</xdr:colOff>
+      <xdr:colOff>704855</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>289526</xdr:rowOff>
+      <xdr:rowOff>285716</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2397,9 +2394,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>665797</xdr:colOff>
+      <xdr:colOff>669607</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>287963</xdr:rowOff>
+      <xdr:rowOff>284153</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2441,9 +2438,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>286762</xdr:colOff>
+      <xdr:colOff>282952</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>1921204</xdr:rowOff>
+      <xdr:rowOff>1925014</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3148,7 +3145,7 @@
       <c r="D26" s="47"/>
       <c r="E26" s="45"/>
       <c r="F26" s="82" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="G26" s="106" t="s">
         <v>134</v>
@@ -3252,7 +3249,7 @@
       </c>
       <c r="C31" s="15" t="str">
         <f>F26</f>
-        <v>LMT_55</v>
+        <v>Pharmed</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="16" t="e">
@@ -3959,36 +3956,36 @@
       <c r="J19" s="86"/>
     </row>
     <row r="20" spans="1:10" s="28" customFormat="1" ht="30.45" customHeight="1">
-      <c r="A20" s="125" t="s">
+      <c r="A20" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="129" t="s">
+      <c r="B20" s="125" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="130"/>
-      <c r="D20" s="130"/>
-      <c r="E20" s="131"/>
+      <c r="C20" s="126"/>
+      <c r="D20" s="126"/>
+      <c r="E20" s="127"/>
       <c r="F20" s="108" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="135" t="s">
+      <c r="G20" s="131" t="s">
         <v>46</v>
       </c>
-      <c r="H20" s="136"/>
-      <c r="I20" s="139" t="s">
+      <c r="H20" s="132"/>
+      <c r="I20" s="135" t="s">
         <v>53</v>
       </c>
-      <c r="J20" s="140"/>
+      <c r="J20" s="136"/>
     </row>
     <row r="21" spans="1:10" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A21" s="125"/>
-      <c r="B21" s="132"/>
-      <c r="C21" s="133"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="134"/>
+      <c r="A21" s="139"/>
+      <c r="B21" s="128"/>
+      <c r="C21" s="129"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="130"/>
       <c r="F21" s="108"/>
-      <c r="G21" s="137"/>
-      <c r="H21" s="138"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="134"/>
       <c r="I21" s="43" t="s">
         <v>47</v>
       </c>
@@ -4000,17 +3997,17 @@
       <c r="A22" s="30">
         <v>1</v>
       </c>
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="123"/>
-      <c r="D22" s="123"/>
-      <c r="E22" s="124"/>
+      <c r="C22" s="120"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="121"/>
       <c r="F22" s="32"/>
-      <c r="G22" s="120" t="s">
+      <c r="G22" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="121"/>
+      <c r="H22" s="138"/>
       <c r="I22" s="33"/>
       <c r="J22" s="92"/>
     </row>
@@ -4018,17 +4015,17 @@
       <c r="A23" s="32">
         <v>2</v>
       </c>
-      <c r="B23" s="122" t="s">
+      <c r="B23" s="119" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="123"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="124"/>
+      <c r="C23" s="120"/>
+      <c r="D23" s="120"/>
+      <c r="E23" s="121"/>
       <c r="F23" s="35"/>
-      <c r="G23" s="120" t="s">
+      <c r="G23" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="121"/>
+      <c r="H23" s="138"/>
       <c r="I23" s="35"/>
       <c r="J23" s="93"/>
     </row>
@@ -4036,17 +4033,17 @@
       <c r="A24" s="32">
         <v>3</v>
       </c>
-      <c r="B24" s="122" t="s">
+      <c r="B24" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="123"/>
-      <c r="D24" s="123"/>
-      <c r="E24" s="124"/>
+      <c r="C24" s="120"/>
+      <c r="D24" s="120"/>
+      <c r="E24" s="121"/>
       <c r="F24" s="35"/>
-      <c r="G24" s="120" t="s">
+      <c r="G24" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="121"/>
+      <c r="H24" s="138"/>
       <c r="I24" s="35"/>
       <c r="J24" s="93"/>
     </row>
@@ -4054,17 +4051,17 @@
       <c r="A25" s="32">
         <v>4</v>
       </c>
-      <c r="B25" s="122" t="s">
+      <c r="B25" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="123"/>
-      <c r="D25" s="123"/>
-      <c r="E25" s="124"/>
+      <c r="C25" s="120"/>
+      <c r="D25" s="120"/>
+      <c r="E25" s="121"/>
       <c r="F25" s="36"/>
-      <c r="G25" s="120" t="s">
+      <c r="G25" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="121"/>
+      <c r="H25" s="138"/>
       <c r="I25" s="35"/>
       <c r="J25" s="93"/>
     </row>
@@ -4072,17 +4069,17 @@
       <c r="A26" s="32">
         <v>5</v>
       </c>
-      <c r="B26" s="122" t="s">
+      <c r="B26" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="123"/>
-      <c r="D26" s="123"/>
-      <c r="E26" s="124"/>
+      <c r="C26" s="120"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="121"/>
       <c r="F26" s="37"/>
-      <c r="G26" s="120" t="s">
+      <c r="G26" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="H26" s="121"/>
+      <c r="H26" s="138"/>
       <c r="I26" s="35"/>
       <c r="J26" s="93"/>
     </row>
@@ -4090,17 +4087,17 @@
       <c r="A27" s="32">
         <v>6</v>
       </c>
-      <c r="B27" s="122" t="s">
+      <c r="B27" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="123"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="124"/>
+      <c r="C27" s="120"/>
+      <c r="D27" s="120"/>
+      <c r="E27" s="121"/>
       <c r="F27" s="37"/>
-      <c r="G27" s="120" t="s">
+      <c r="G27" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="121"/>
+      <c r="H27" s="138"/>
       <c r="I27" s="35"/>
       <c r="J27" s="93"/>
     </row>
@@ -4108,17 +4105,17 @@
       <c r="A28" s="32">
         <v>7</v>
       </c>
-      <c r="B28" s="122" t="s">
+      <c r="B28" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="123"/>
-      <c r="D28" s="123"/>
-      <c r="E28" s="124"/>
+      <c r="C28" s="120"/>
+      <c r="D28" s="120"/>
+      <c r="E28" s="121"/>
       <c r="F28" s="37"/>
-      <c r="G28" s="120" t="s">
+      <c r="G28" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="H28" s="121"/>
+      <c r="H28" s="138"/>
       <c r="I28" s="35"/>
       <c r="J28" s="93"/>
     </row>
@@ -4126,17 +4123,17 @@
       <c r="A29" s="37">
         <v>8</v>
       </c>
-      <c r="B29" s="122" t="s">
+      <c r="B29" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="123"/>
-      <c r="D29" s="123"/>
-      <c r="E29" s="124"/>
+      <c r="C29" s="120"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="121"/>
       <c r="F29" s="31"/>
-      <c r="G29" s="120" t="s">
+      <c r="G29" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="121"/>
+      <c r="H29" s="138"/>
       <c r="I29" s="35"/>
       <c r="J29" s="93"/>
     </row>
@@ -4144,17 +4141,17 @@
       <c r="A30" s="37">
         <v>9</v>
       </c>
-      <c r="B30" s="122" t="s">
+      <c r="B30" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="123"/>
-      <c r="D30" s="123"/>
-      <c r="E30" s="124"/>
+      <c r="C30" s="120"/>
+      <c r="D30" s="120"/>
+      <c r="E30" s="121"/>
       <c r="F30" s="31"/>
-      <c r="G30" s="120" t="s">
+      <c r="G30" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="121"/>
+      <c r="H30" s="138"/>
       <c r="I30" s="35"/>
       <c r="J30" s="93"/>
     </row>
@@ -4162,17 +4159,17 @@
       <c r="A31" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="126" t="s">
+      <c r="B31" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="127"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="128"/>
+      <c r="C31" s="123"/>
+      <c r="D31" s="123"/>
+      <c r="E31" s="124"/>
       <c r="F31" s="31"/>
-      <c r="G31" s="120" t="s">
+      <c r="G31" s="137" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="121"/>
+      <c r="H31" s="138"/>
       <c r="I31" s="35"/>
       <c r="J31" s="93"/>
     </row>
@@ -4225,21 +4222,21 @@
       <c r="J35" s="86"/>
     </row>
     <row r="36" spans="1:13" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="119" t="s">
+      <c r="A36" s="140" t="s">
         <v>64</v>
       </c>
-      <c r="B36" s="119"/>
-      <c r="C36" s="119"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="119"/>
-      <c r="H36" s="119"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="119"/>
-      <c r="K36" s="119"/>
-      <c r="L36" s="119"/>
-      <c r="M36" s="119"/>
+      <c r="B36" s="140"/>
+      <c r="C36" s="140"/>
+      <c r="D36" s="140"/>
+      <c r="E36" s="140"/>
+      <c r="F36" s="140"/>
+      <c r="G36" s="140"/>
+      <c r="H36" s="140"/>
+      <c r="I36" s="140"/>
+      <c r="J36" s="140"/>
+      <c r="K36" s="140"/>
+      <c r="L36" s="140"/>
+      <c r="M36" s="140"/>
     </row>
     <row r="37" spans="1:13" s="28" customFormat="1" ht="40.950000000000003" customHeight="1">
       <c r="A37" s="72" t="s">
@@ -4293,7 +4290,7 @@
         <v>2.72</v>
       </c>
       <c r="D38" s="73" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="E38" s="103"/>
       <c r="F38" s="103"/>
@@ -4356,7 +4353,9 @@
       <c r="C40" s="73">
         <v>2.84</v>
       </c>
-      <c r="D40" s="73"/>
+      <c r="D40" s="73" t="s">
+        <v>125</v>
+      </c>
       <c r="E40" s="103"/>
       <c r="F40" s="104"/>
       <c r="G40" s="73">
@@ -4450,7 +4449,9 @@
         <v>3.45</v>
       </c>
       <c r="D43" s="73"/>
-      <c r="E43" s="104"/>
+      <c r="E43" s="104" t="s">
+        <v>121</v>
+      </c>
       <c r="F43" s="105"/>
       <c r="G43" s="73">
         <v>152</v>
@@ -4482,7 +4483,9 @@
       </c>
       <c r="D44" s="73"/>
       <c r="E44" s="103"/>
-      <c r="F44" s="103"/>
+      <c r="F44" s="103" t="s">
+        <v>128</v>
+      </c>
       <c r="G44" s="73">
         <v>152</v>
       </c>
@@ -4551,19 +4554,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B20:E21"/>
-    <mergeCell ref="G20:H21"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A1:J5"/>
-    <mergeCell ref="B22:E22"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="H36:M36"/>
     <mergeCell ref="G30:H30"/>
@@ -4580,6 +4570,19 @@
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B29:E29"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A1:J5"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B20:E21"/>
+    <mergeCell ref="G20:H21"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B23:E23"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.51181102362204722" right="0.11811023622047245" top="0.35433070866141736" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4590,7 +4593,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FF915FA9-662F-4BBC-ACDC-22805800E086}">
           <x14:formula1>
-            <xm:f>INDIRECT('A1'!F26)</xm:f>
+            <xm:f>INDIRECT('A1'!$F$26)</xm:f>
           </x14:formula1>
           <xm:sqref>D38:F45</xm:sqref>
         </x14:dataValidation>

--- a/examples/TAAT/ใบสั่งงาน TAAT.xlsx
+++ b/examples/TAAT/ใบสั่งงาน TAAT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vatska\software\examples\TAAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17C9108-E61C-4C85-A699-1E624C8B9206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B46D464-DBF4-401F-B0AD-D9D540CC8AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{874D8AF1-DF56-4DEE-86B1-A5E2F5D42D71}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="136">
   <si>
     <r>
       <t>บริษัท แวตสก้า จำกัด/ Vatska Company Limited</t>
@@ -489,7 +489,7 @@
     <t>What if " LMT55, Pharmed or E3603" then show dropdown list" worksheet A2, column D,E,F -line 38-48</t>
   </si>
   <si>
-    <t>LMT_55</t>
+    <t>A053404-EP-CP</t>
   </si>
 </sst>
 </file>
@@ -1739,7 +1739,7 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>685804</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>324768</xdr:rowOff>
+      <xdr:rowOff>320958</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1781,7 +1781,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>701040</xdr:colOff>
+      <xdr:colOff>704850</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>932</xdr:rowOff>
     </xdr:to>
@@ -1825,9 +1825,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>708133</xdr:colOff>
+      <xdr:colOff>704323</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>286703</xdr:rowOff>
+      <xdr:rowOff>282893</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1869,9 +1869,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>701992</xdr:colOff>
+      <xdr:colOff>705802</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>287839</xdr:rowOff>
+      <xdr:rowOff>284029</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1913,7 +1913,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>704850</xdr:colOff>
+      <xdr:colOff>701040</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>121</xdr:rowOff>
     </xdr:to>
@@ -1957,7 +1957,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>702945</xdr:colOff>
+      <xdr:colOff>706755</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>2086</xdr:rowOff>
     </xdr:to>
@@ -2001,9 +2001,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>705277</xdr:colOff>
+      <xdr:colOff>701467</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>288608</xdr:rowOff>
+      <xdr:rowOff>284798</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2045,7 +2045,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>705802</xdr:colOff>
+      <xdr:colOff>701992</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>2527</xdr:rowOff>
     </xdr:to>
@@ -2091,7 +2091,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>689085</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>284798</xdr:rowOff>
+      <xdr:rowOff>288608</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2133,7 +2133,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>705803</xdr:colOff>
+      <xdr:colOff>701993</xdr:colOff>
       <xdr:row>38</xdr:row>
       <xdr:rowOff>184</xdr:rowOff>
     </xdr:to>
@@ -2177,9 +2177,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>705276</xdr:colOff>
+      <xdr:colOff>701466</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>283366</xdr:rowOff>
+      <xdr:rowOff>287176</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2221,7 +2221,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>707707</xdr:colOff>
+      <xdr:colOff>703897</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>121</xdr:rowOff>
     </xdr:to>
@@ -2309,7 +2309,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>707707</xdr:colOff>
+      <xdr:colOff>703897</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>304921</xdr:rowOff>
     </xdr:to>
@@ -2353,9 +2353,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>701045</xdr:colOff>
+      <xdr:colOff>704855</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>289526</xdr:rowOff>
+      <xdr:rowOff>285716</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2397,9 +2397,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>665797</xdr:colOff>
+      <xdr:colOff>669607</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>287963</xdr:rowOff>
+      <xdr:rowOff>284153</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2441,9 +2441,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>286762</xdr:colOff>
+      <xdr:colOff>282952</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>1921204</xdr:rowOff>
+      <xdr:rowOff>1925014</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2908,7 +2908,9 @@
       <c r="A11" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="69"/>
+      <c r="B11" s="69" t="s">
+        <v>135</v>
+      </c>
       <c r="C11" s="85"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -3148,7 +3150,7 @@
       <c r="D26" s="47"/>
       <c r="E26" s="45"/>
       <c r="F26" s="82" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="G26" s="106" t="s">
         <v>134</v>
@@ -3252,7 +3254,7 @@
       </c>
       <c r="C31" s="15" t="str">
         <f>F26</f>
-        <v>LMT_55</v>
+        <v>Pharmed</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="16" t="e">
@@ -4293,7 +4295,7 @@
         <v>2.72</v>
       </c>
       <c r="D38" s="73" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="E38" s="103"/>
       <c r="F38" s="103"/>
@@ -4356,7 +4358,9 @@
       <c r="C40" s="73">
         <v>2.84</v>
       </c>
-      <c r="D40" s="73"/>
+      <c r="D40" s="73" t="s">
+        <v>125</v>
+      </c>
       <c r="E40" s="103"/>
       <c r="F40" s="104"/>
       <c r="G40" s="73">
@@ -4450,7 +4454,9 @@
         <v>3.45</v>
       </c>
       <c r="D43" s="73"/>
-      <c r="E43" s="104"/>
+      <c r="E43" s="104" t="s">
+        <v>121</v>
+      </c>
       <c r="F43" s="105"/>
       <c r="G43" s="73">
         <v>152</v>
@@ -4482,7 +4488,9 @@
       </c>
       <c r="D44" s="73"/>
       <c r="E44" s="103"/>
-      <c r="F44" s="103"/>
+      <c r="F44" s="103" t="s">
+        <v>128</v>
+      </c>
       <c r="G44" s="73">
         <v>152</v>
       </c>
@@ -4590,7 +4598,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FF915FA9-662F-4BBC-ACDC-22805800E086}">
           <x14:formula1>
-            <xm:f>INDIRECT('A1'!F26)</xm:f>
+            <xm:f>INDIRECT('A1'!$F$26)</xm:f>
           </x14:formula1>
           <xm:sqref>D38:F45</xm:sqref>
         </x14:dataValidation>

--- a/examples/TAAT/ใบสั่งงาน TAAT.xlsx
+++ b/examples/TAAT/ใบสั่งงาน TAAT.xlsx
@@ -8,7 +8,8 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vatska\software\examples\TAAT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B46D464-DBF4-401F-B0AD-D9D540CC8AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F563907-9B3F-47B9-830C-9EDCD46D76C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="TmhOUAbV6Mao4qBQ9X4XIXpPawG26JcP8MgNdAljK+SMlr44TvcDa5UKA30AJq37ev9s6UDcZf4pTl21qxCDhA==" workbookSaltValue="bzDSmLS+e8/8+jbAshl4Ow==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{874D8AF1-DF56-4DEE-86B1-A5E2F5D42D71}"/>
   </bookViews>
@@ -17,9 +18,7 @@
     <sheet name="A2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="E_3603">'A1'!$L$28:$L$38</definedName>
-    <definedName name="LMT_55">'A1'!$K$28:$K$38</definedName>
-    <definedName name="Pharmed">'A1'!$J$28:$J$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'A1'!$A$1:$I$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="140">
   <si>
     <r>
       <t>บริษัท แวตสก้า จำกัด/ Vatska Company Limited</t>
@@ -104,9 +103,6 @@
     <t xml:space="preserve">ถุงพลาสติค </t>
   </si>
   <si>
-    <t>ขวดกาว / ถ้วยสแตนเลสใส่กาว</t>
-  </si>
-  <si>
     <t>คีมหนีบสแตนเลสปากแหลม/ปากแบน</t>
   </si>
   <si>
@@ -216,9 +212,6 @@
   </si>
   <si>
     <t>จำนวนที่ผ่าน/ไม่ผ่านการตรวจสอบ</t>
-  </si>
-  <si>
-    <t>จำนวนที่ผลิต</t>
   </si>
   <si>
     <t>A1</t>
@@ -371,6 +364,93 @@
   </si>
   <si>
     <t>Lot no</t>
+  </si>
+  <si>
+    <t>Pharmed</t>
+  </si>
+  <si>
+    <t>LMT-55</t>
+  </si>
+  <si>
+    <t>E-3603</t>
+  </si>
+  <si>
+    <t>AY242605</t>
+  </si>
+  <si>
+    <t>AY242606</t>
+  </si>
+  <si>
+    <t>AY242607</t>
+  </si>
+  <si>
+    <t>AY242602</t>
+  </si>
+  <si>
+    <t>AY242603</t>
+  </si>
+  <si>
+    <t>ALH00001</t>
+  </si>
+  <si>
+    <t>ALH00002</t>
+  </si>
+  <si>
+    <t>ALH00003</t>
+  </si>
+  <si>
+    <t>ALH00004</t>
+  </si>
+  <si>
+    <t>ALH00005</t>
+  </si>
+  <si>
+    <t>ALH00006</t>
+  </si>
+  <si>
+    <t>ALH02002</t>
+  </si>
+  <si>
+    <t>ALH02004</t>
+  </si>
+  <si>
+    <t>ACF00001</t>
+  </si>
+  <si>
+    <t>ACF00002</t>
+  </si>
+  <si>
+    <t>ACF02002</t>
+  </si>
+  <si>
+    <t>ACF00003</t>
+  </si>
+  <si>
+    <t>ACF00004</t>
+  </si>
+  <si>
+    <t>ACF02004</t>
+  </si>
+  <si>
+    <t>ACF00005</t>
+  </si>
+  <si>
+    <t>ACF00006</t>
+  </si>
+  <si>
+    <t>08-Aug-2026</t>
+  </si>
+  <si>
+    <t>สีของคอลล่าร์  1</t>
+  </si>
+  <si>
+    <t>สีของคอลล่าร์  2</t>
+  </si>
+  <si>
+    <t>สีของคอลล่าร์  3</t>
+  </si>
+  <si>
+    <t>จำนวนชิ้นที่ผลิต</t>
   </si>
   <si>
     <r>
@@ -391,113 +471,45 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">
-53/2 ต. อ้อมเกร็ด อ. ปากเกร็ด จ. นนทบุรี 11120/ 53/2 T. Om-Kred A. Pakkred Nonthaburi 11120 Thailand
+53/2 ต. อ้อมเกร็ด อ. ปากเกร็ด จ. นนทบุรี 11120/ 53/2 T. Om-Kred A. Pakkred Nonthaburi 11120 ThailandA2
 โทร. +662 9244161 อีเมล: sales@vatska.com/ Tel: +662 9244161 E-mail: sales@vatska.com </t>
     </r>
   </si>
   <si>
-    <t>Pharmed</t>
-  </si>
-  <si>
-    <t>LMT-55</t>
-  </si>
-  <si>
-    <t>E-3603</t>
-  </si>
-  <si>
-    <t>AY242605</t>
-  </si>
-  <si>
-    <t>AY242606</t>
-  </si>
-  <si>
-    <t>AY242607</t>
-  </si>
-  <si>
-    <t>AY242602</t>
-  </si>
-  <si>
-    <t>AY242603</t>
-  </si>
-  <si>
-    <t>ALH00001</t>
-  </si>
-  <si>
-    <t>ALH00002</t>
-  </si>
-  <si>
-    <t>ALH00003</t>
-  </si>
-  <si>
-    <t>ALH00004</t>
-  </si>
-  <si>
-    <t>ALH00005</t>
-  </si>
-  <si>
-    <t>ALH00006</t>
-  </si>
-  <si>
-    <t>ALH00007</t>
-  </si>
-  <si>
-    <t>ALH00008</t>
-  </si>
-  <si>
-    <t>ALH02002</t>
-  </si>
-  <si>
-    <t>ALH02004</t>
-  </si>
-  <si>
-    <t>ALH4006</t>
-  </si>
-  <si>
-    <t>ACF00001</t>
-  </si>
-  <si>
-    <t>ACF00002</t>
-  </si>
-  <si>
-    <t>ACF02002</t>
-  </si>
-  <si>
-    <t>ACF00003</t>
-  </si>
-  <si>
-    <t>ACF00004</t>
-  </si>
-  <si>
-    <t>ACF02004</t>
-  </si>
-  <si>
-    <t>ACF00005</t>
-  </si>
-  <si>
-    <t>ACF00006</t>
-  </si>
-  <si>
-    <t>ACF00007</t>
-  </si>
-  <si>
-    <t>ACF04006</t>
-  </si>
-  <si>
-    <t>ACF02007</t>
-  </si>
-  <si>
-    <t>What if " LMT55, Pharmed or E3603" then show dropdown list" worksheet A2, column D,E,F -line 38-48</t>
+    <t>LOCTITE</t>
   </si>
   <si>
     <t>A053404-EP-CP</t>
+  </si>
+  <si>
+    <t>ACF49258</t>
+  </si>
+  <si>
+    <t>เหลือง</t>
+  </si>
+  <si>
+    <t>AMTEC867</t>
+  </si>
+  <si>
+    <t>AMWEC867</t>
+  </si>
+  <si>
+    <t>002/20260820</t>
+  </si>
+  <si>
+    <t>จำนวนที่ใช้</t>
+  </si>
+  <si>
+    <t>TAAT Tygon E-3603,0.44mmIDx0.89mmWallx381mmL,  2 stoppers Green Yellow,152mmStoppers Distance,</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -839,15 +851,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -971,18 +980,12 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -992,17 +995,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1093,9 +1087,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1103,8 +1094,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1114,16 +1103,43 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1151,7 +1167,64 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1160,61 +1233,10 @@
     <xf numFmtId="164" fontId="15" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1401,13 +1423,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>1040693</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>238123</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>16037</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1476,7 +1498,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>506789</xdr:colOff>
+      <xdr:colOff>835494</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>69191</xdr:rowOff>
     </xdr:to>
@@ -1524,8 +1546,8 @@
       <xdr:rowOff>90488</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1066800</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>111124</xdr:rowOff>
     </xdr:to>
@@ -1564,68 +1586,6 @@
         <a:noFill/>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>546100</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64FBE1AB-5620-4A9D-BF32-3A36826728E9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8197850" y="63500"/>
-          <a:ext cx="527050" cy="482600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="6350"/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -1739,7 +1699,7 @@
       <xdr:col>9</xdr:col>
       <xdr:colOff>685804</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>320958</xdr:rowOff>
+      <xdr:rowOff>309528</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1781,9 +1741,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>704850</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>932</xdr:rowOff>
+      <xdr:colOff>695325</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>313352</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1825,9 +1785,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>704323</xdr:colOff>
+      <xdr:colOff>708133</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>282893</xdr:rowOff>
+      <xdr:rowOff>271463</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1869,9 +1829,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>705802</xdr:colOff>
+      <xdr:colOff>709612</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>284029</xdr:rowOff>
+      <xdr:rowOff>287839</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1913,7 +1873,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>701040</xdr:colOff>
+      <xdr:colOff>704850</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>121</xdr:rowOff>
     </xdr:to>
@@ -1957,7 +1917,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>706755</xdr:colOff>
+      <xdr:colOff>714375</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>2086</xdr:rowOff>
     </xdr:to>
@@ -2001,9 +1961,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>701467</xdr:colOff>
+      <xdr:colOff>693847</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>284798</xdr:rowOff>
+      <xdr:rowOff>280988</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2045,9 +2005,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>701992</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>2527</xdr:rowOff>
+      <xdr:colOff>690562</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>318757</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2091,7 +2051,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>689085</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>288608</xdr:rowOff>
+      <xdr:rowOff>300038</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2133,9 +2093,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>701993</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>184</xdr:rowOff>
+      <xdr:colOff>690563</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>316414</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2177,9 +2137,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>701466</xdr:colOff>
+      <xdr:colOff>693846</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>287176</xdr:rowOff>
+      <xdr:rowOff>290986</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2221,9 +2181,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>703897</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>121</xdr:rowOff>
+      <xdr:colOff>700087</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>314446</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2266,8 +2226,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>685799</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>1574</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>313994</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2309,7 +2269,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>703897</xdr:colOff>
+      <xdr:colOff>700087</xdr:colOff>
       <xdr:row>43</xdr:row>
       <xdr:rowOff>304921</xdr:rowOff>
     </xdr:to>
@@ -2353,9 +2313,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>704855</xdr:colOff>
+      <xdr:colOff>695330</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>285716</xdr:rowOff>
+      <xdr:rowOff>295241</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2397,9 +2357,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>669607</xdr:colOff>
+      <xdr:colOff>681037</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>284153</xdr:rowOff>
+      <xdr:rowOff>297488</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2441,9 +2401,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>282952</xdr:colOff>
+      <xdr:colOff>271522</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>1925014</xdr:rowOff>
+      <xdr:rowOff>1928824</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2474,6 +2434,76 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>881063</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>128588</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>538163</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{663F8C40-6AEA-6096-CA44-88A3EB80B0CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11329988" y="128588"/>
+          <a:ext cx="628650" cy="671512"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="2800"/>
+            <a:t>A2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2780,22 +2810,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD76B8CF-98AE-4DC9-9DC6-C45CB37DF509}">
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
   <cols>
     <col min="1" max="1" width="14.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.21875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="35.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.21875" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="49" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" style="48" customWidth="1"/>
     <col min="9" max="16384" width="8" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.5" customHeight="1"/>
-    <row r="2" spans="1:8" ht="25.95" customHeight="1">
+    <row r="1" spans="1:11" ht="16.5" customHeight="1"/>
+    <row r="2" spans="1:11" ht="25.95" customHeight="1">
       <c r="B2" s="111" t="s">
         <v>0</v>
       </c>
@@ -2804,49 +2834,49 @@
       <c r="E2" s="111"/>
       <c r="F2" s="111"/>
       <c r="G2" s="111"/>
-      <c r="H2" s="57" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="12" customHeight="1">
+      <c r="H2" s="54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="12" customHeight="1">
       <c r="B3" s="111"/>
       <c r="C3" s="111"/>
       <c r="D3" s="111"/>
       <c r="E3" s="111"/>
       <c r="F3" s="111"/>
       <c r="G3" s="111"/>
-      <c r="H3" s="50"/>
-    </row>
-    <row r="4" spans="1:8" ht="12" customHeight="1">
+      <c r="H3" s="49"/>
+    </row>
+    <row r="4" spans="1:11" ht="12" customHeight="1">
       <c r="B4" s="111"/>
       <c r="C4" s="111"/>
       <c r="D4" s="111"/>
       <c r="E4" s="111"/>
       <c r="F4" s="111"/>
       <c r="G4" s="111"/>
-      <c r="H4" s="50"/>
-    </row>
-    <row r="5" spans="1:8" ht="12" customHeight="1">
+      <c r="H4" s="49"/>
+    </row>
+    <row r="5" spans="1:11" ht="12" customHeight="1">
       <c r="B5" s="111"/>
       <c r="C5" s="111"/>
       <c r="D5" s="111"/>
       <c r="E5" s="111"/>
       <c r="F5" s="111"/>
       <c r="G5" s="111"/>
-      <c r="H5" s="50"/>
-    </row>
-    <row r="6" spans="1:8" ht="12" customHeight="1">
+      <c r="H5" s="49"/>
+    </row>
+    <row r="6" spans="1:11" ht="12" customHeight="1">
       <c r="B6" s="111"/>
       <c r="C6" s="111"/>
       <c r="D6" s="111"/>
       <c r="E6" s="111"/>
       <c r="F6" s="111"/>
       <c r="G6" s="111"/>
-      <c r="H6" s="50"/>
-    </row>
-    <row r="7" spans="1:8" ht="55.95" customHeight="1">
+      <c r="H6" s="49"/>
+    </row>
+    <row r="7" spans="1:11" ht="55.95" customHeight="1">
       <c r="A7" s="110" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="110"/>
       <c r="C7" s="110"/>
@@ -2854,346 +2884,352 @@
       <c r="E7" s="110"/>
       <c r="F7" s="110"/>
       <c r="G7" s="110"/>
-      <c r="H7" s="51"/>
-    </row>
-    <row r="8" spans="1:8" s="11" customFormat="1" ht="21" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="H7" s="50"/>
+      <c r="K7" s="48"/>
+    </row>
+    <row r="8" spans="1:11" s="10" customFormat="1" ht="21" customHeight="1">
+      <c r="A8" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="107">
-        <v>46238</v>
-      </c>
-      <c r="F8" s="64" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="67" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="66"/>
-    </row>
-    <row r="9" spans="1:8" s="11" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="B8" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="60"/>
+    </row>
+    <row r="9" spans="1:11" s="10" customFormat="1" ht="21" customHeight="1">
+      <c r="A9" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10" t="s">
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="78">
+        <v>123450</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="10" customFormat="1" ht="21" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="119" t="s">
+        <v>129</v>
+      </c>
+      <c r="G10" s="119"/>
+      <c r="H10" s="62">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="10" customFormat="1" ht="21" customHeight="1">
+      <c r="A11" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="63"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="101" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="10" customFormat="1" ht="21" customHeight="1">
+      <c r="A12" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="B12" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="98"/>
+      <c r="F12" s="120" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="120"/>
+      <c r="H12" s="62">
         <v>12</v>
       </c>
-      <c r="H9" s="84"/>
-    </row>
-    <row r="10" spans="1:8" s="11" customFormat="1" ht="21" customHeight="1">
-      <c r="A10" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="65" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="68">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="11" customFormat="1" ht="21" customHeight="1">
-      <c r="A11" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="C11" s="85"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="65" t="s">
-        <v>99</v>
-      </c>
-      <c r="H11" s="68"/>
-    </row>
-    <row r="12" spans="1:8" s="11" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="69"/>
-      <c r="D12" s="109" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" s="109"/>
-      <c r="F12" s="109"/>
-      <c r="H12" s="68"/>
-    </row>
-    <row r="13" spans="1:8" s="28" customFormat="1" ht="37.5" customHeight="1">
-      <c r="A13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26" t="s">
+    </row>
+    <row r="13" spans="1:11" s="27" customFormat="1" ht="37.5" customHeight="1">
+      <c r="A13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="26"/>
-      <c r="H13" s="83"/>
-    </row>
-    <row r="14" spans="1:8" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="52"/>
-    </row>
-    <row r="15" spans="1:8" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="52"/>
-    </row>
-    <row r="16" spans="1:8" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="52"/>
-    </row>
-    <row r="17" spans="1:12" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="52"/>
-    </row>
-    <row r="18" spans="1:12" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="52"/>
-    </row>
-    <row r="19" spans="1:12" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="75" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="70">
+      <c r="G13" s="25"/>
+      <c r="H13" s="77"/>
+    </row>
+    <row r="14" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="51"/>
+    </row>
+    <row r="15" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="51"/>
+    </row>
+    <row r="16" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="51"/>
+    </row>
+    <row r="17" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="51"/>
+    </row>
+    <row r="18" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="51"/>
+    </row>
+    <row r="19" spans="1:11" s="5" customFormat="1" ht="21" customHeight="1">
+      <c r="A19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="64">
         <v>381</v>
       </c>
-      <c r="D19" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="70">
+      <c r="D19" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="64">
         <f>C19-F19</f>
         <v>368.3</v>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="47">
         <v>12.7</v>
       </c>
-      <c r="G19" s="60">
+      <c r="G19" s="102">
         <f>C19-F19</f>
         <v>368.3</v>
       </c>
-      <c r="H19" s="53">
+      <c r="H19" s="103">
         <f>C19+F19</f>
         <v>393.7</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A20" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="75" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="71">
+    <row r="20" spans="1:11" s="5" customFormat="1" ht="21" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="69" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="65">
         <v>114.3</v>
       </c>
-      <c r="D20" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="70">
+      <c r="D20" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="64">
         <f>C20-F20</f>
         <v>107.95</v>
       </c>
-      <c r="F20" s="48">
+      <c r="F20" s="47">
         <v>6.35</v>
       </c>
-      <c r="G20" s="60">
+      <c r="G20" s="102">
         <f t="shared" ref="G20:G21" si="0">C20-F20</f>
         <v>107.95</v>
       </c>
-      <c r="H20" s="53">
+      <c r="H20" s="103">
         <f t="shared" ref="H20:H21" si="1">C20+F20</f>
         <v>120.64999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:11" s="5" customFormat="1" ht="21" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="65">
+        <v>151.88999999999999</v>
+      </c>
+      <c r="D21" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="71">
-        <v>151.88999999999999</v>
-      </c>
-      <c r="D21" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="70">
+      <c r="E21" s="64">
         <f>C21-F21</f>
         <v>150.36999999999998</v>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="47">
         <v>1.52</v>
       </c>
-      <c r="G21" s="60">
+      <c r="G21" s="102">
         <f t="shared" si="0"/>
         <v>150.36999999999998</v>
       </c>
-      <c r="H21" s="53">
+      <c r="H21" s="103">
         <f t="shared" si="1"/>
         <v>153.41</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="6" customFormat="1" ht="39.75" customHeight="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6" t="s">
+    <row r="22" spans="1:11" s="5" customFormat="1" ht="39.75" customHeight="1">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="93">
+        <v>3</v>
+      </c>
+      <c r="D22" s="105" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="F22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="100">
-        <v>2</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="48"/>
-    </row>
-    <row r="23" spans="1:12" s="46" customFormat="1" ht="16.05" customHeight="1">
-      <c r="A23" s="45" t="s">
+      <c r="H22" s="47"/>
+    </row>
+    <row r="23" spans="1:11" s="45" customFormat="1" ht="16.05" customHeight="1">
+      <c r="A23" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="46">
+        <f>H10*1</f>
+        <v>300</v>
+      </c>
+      <c r="E23" s="44"/>
+      <c r="F23" s="76" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" s="104" t="str">
+        <f>_xlfn.XLOOKUP(F23,'A2'!L38:L46,'A2'!K38:K46,0,0)</f>
+        <v>AMWEC867</v>
+      </c>
+      <c r="H23" s="52"/>
+    </row>
+    <row r="24" spans="1:11" s="45" customFormat="1" ht="16.05" customHeight="1">
+      <c r="A24" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="46">
+        <f>H10*1</f>
+        <v>300</v>
+      </c>
+      <c r="E24" s="44"/>
+      <c r="F24" s="76" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="104" t="str">
+        <f>_xlfn.XLOOKUP(F24,'A2'!L38:L46,'A2'!K38:K46,0,0)</f>
+        <v>AYIEC871</v>
+      </c>
+      <c r="H24" s="52"/>
+    </row>
+    <row r="25" spans="1:11" s="45" customFormat="1" ht="16.05" customHeight="1">
+      <c r="A25" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="47"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="82" t="s">
-        <v>93</v>
-      </c>
-      <c r="G23" s="47" t="str">
-        <f>_xlfn.XLOOKUP(F23,'A2'!L38:L45,'A2'!K38:K45,0,0)</f>
-        <v xml:space="preserve">AYHEC871 </v>
-      </c>
-      <c r="H23" s="54"/>
-    </row>
-    <row r="24" spans="1:12" s="46" customFormat="1" ht="16.05" customHeight="1">
-      <c r="A24" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="47"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="82" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="47" t="str">
-        <f>_xlfn.XLOOKUP(F24,'A2'!L38:L45,'A2'!K38:K45,0,0)</f>
-        <v>AYFEC869</v>
-      </c>
-      <c r="H24" s="54"/>
-    </row>
-    <row r="25" spans="1:12" s="46" customFormat="1" ht="16.05" customHeight="1">
-      <c r="A25" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="B25" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="47"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="82" t="s">
-        <v>90</v>
-      </c>
-      <c r="G25" s="47" t="str">
-        <f>_xlfn.XLOOKUP(F25,'A2'!L38:L45,'A2'!K38:K45,0,0)</f>
-        <v>AYIEC871</v>
-      </c>
-      <c r="H25" s="54"/>
-    </row>
-    <row r="26" spans="1:12" s="46" customFormat="1" ht="16.05" customHeight="1">
-      <c r="A26" s="45" t="s">
+      <c r="B25" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="46">
+        <f>H10*G25</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="44"/>
+      <c r="F25" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="104">
+        <f>_xlfn.XLOOKUP(F25,'A2'!L38:L46,'A2'!K38:K46,0,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="52"/>
+    </row>
+    <row r="26" spans="1:11" s="45" customFormat="1" ht="16.05" customHeight="1">
+      <c r="A26" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" s="47"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="82" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" s="106" t="s">
-        <v>134</v>
-      </c>
-      <c r="H26" s="54"/>
-    </row>
-    <row r="27" spans="1:12" s="11" customFormat="1" ht="36" customHeight="1">
-      <c r="A27" s="13" t="s">
+      <c r="B26" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="46"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="99" t="s">
+        <v>133</v>
+      </c>
+      <c r="K26" s="45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" s="10" customFormat="1" ht="36" customHeight="1">
+      <c r="A27" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="44"/>
-      <c r="J27" s="72" t="s">
-        <v>104</v>
-      </c>
-      <c r="K27" s="72" t="s">
-        <v>105</v>
-      </c>
-      <c r="L27" s="72" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
-      <c r="A28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="44"/>
-      <c r="J28" s="73" t="s">
-        <v>107</v>
-      </c>
-      <c r="K28" s="103" t="s">
-        <v>112</v>
-      </c>
-      <c r="L28" s="103" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="43"/>
+    </row>
+    <row r="28" spans="1:11" s="10" customFormat="1" ht="21" customHeight="1">
+      <c r="A28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="43"/>
+    </row>
+    <row r="29" spans="1:11" s="10" customFormat="1" ht="21" customHeight="1">
       <c r="A29" s="112" t="s">
         <v>5</v>
       </c>
@@ -3201,32 +3237,23 @@
         <v>6</v>
       </c>
       <c r="C29" s="112" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29" s="112" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E29" s="115" t="s">
         <v>7</v>
       </c>
       <c r="F29" s="117" t="s">
+        <v>50</v>
+      </c>
+      <c r="G29" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="G29" s="108" t="s">
-        <v>52</v>
-      </c>
-      <c r="H29" s="108"/>
-      <c r="J29" s="73" t="s">
-        <v>108</v>
-      </c>
-      <c r="K29" s="103" t="s">
-        <v>113</v>
-      </c>
-      <c r="L29" s="103" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
+      <c r="H29" s="109"/>
+    </row>
+    <row r="30" spans="1:11" s="10" customFormat="1" ht="21" customHeight="1">
       <c r="A30" s="112"/>
       <c r="B30" s="114"/>
       <c r="C30" s="112"/>
@@ -3234,421 +3261,352 @@
       <c r="E30" s="116"/>
       <c r="F30" s="118"/>
       <c r="G30" s="115"/>
-      <c r="H30" s="108"/>
-      <c r="J30" s="73" t="s">
-        <v>110</v>
-      </c>
-      <c r="K30" s="103" t="s">
-        <v>120</v>
-      </c>
-      <c r="L30" s="104" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="7">
+      <c r="H30" s="109"/>
+    </row>
+    <row r="31" spans="1:11" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A31" s="6">
         <v>1</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="15" t="str">
+      <c r="C31" s="71" t="str">
         <f>F26</f>
-        <v>Pharmed</v>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="16" t="e">
+        <v>E-3603</v>
+      </c>
+      <c r="D31" s="71" t="str">
+        <f>G26</f>
+        <v>ACF49258</v>
+      </c>
+      <c r="E31" s="15" t="e">
         <f>D31*#REF!*(#REF!+#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F31" s="61" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="58" t="s">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F31" s="106">
+        <f>H10*C19*0.00328/25</f>
+        <v>14.99616</v>
+      </c>
+      <c r="G31" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" s="57"/>
+    </row>
+    <row r="32" spans="1:11" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A32" s="7">
+        <v>2</v>
+      </c>
+      <c r="B32" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="H31" s="62"/>
-      <c r="J31" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="K31" s="103" t="s">
-        <v>114</v>
-      </c>
-      <c r="L31" s="103" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="8">
-        <v>2</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="81" t="str">
+      <c r="C32" s="75" t="str">
         <f t="shared" ref="C32:D34" si="2">F23</f>
-        <v>ฟ้า</v>
-      </c>
-      <c r="D32" s="78" t="str">
+        <v>เหลือง</v>
+      </c>
+      <c r="D32" s="72" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">AYHEC871 </v>
-      </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15">
-        <f>H10*1</f>
+        <v>AMWEC867</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="107">
+        <f>D23</f>
         <v>300</v>
       </c>
-      <c r="G32" s="15" t="s">
+      <c r="G32" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32" s="57"/>
+    </row>
+    <row r="33" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A33" s="7"/>
+      <c r="B33" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="H32" s="62"/>
-      <c r="J32" s="73" t="s">
-        <v>107</v>
-      </c>
-      <c r="K32" s="103" t="s">
-        <v>115</v>
-      </c>
-      <c r="L32" s="103" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="81" t="str">
-        <f t="shared" si="2"/>
-        <v>ดำ</v>
-      </c>
-      <c r="D33" s="79" t="str">
-        <f t="shared" si="2"/>
-        <v>AYFEC869</v>
-      </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15">
-        <f>H10*1</f>
-        <v>300</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H33" s="62"/>
-      <c r="J33" s="73" t="s">
-        <v>108</v>
-      </c>
-      <c r="K33" s="104" t="s">
-        <v>121</v>
-      </c>
-      <c r="L33" s="105" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C34" s="77" t="str">
+      <c r="C33" s="75" t="str">
         <f t="shared" si="2"/>
         <v>เขียว</v>
       </c>
-      <c r="D34" s="80" t="str">
+      <c r="D33" s="73" t="str">
         <f t="shared" si="2"/>
         <v>AYIEC871</v>
       </c>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15">
-        <f>H10*1</f>
+      <c r="E33" s="14"/>
+      <c r="F33" s="107">
+        <f>D24</f>
         <v>300</v>
       </c>
-      <c r="G34" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H34" s="62"/>
-      <c r="J34" s="73" t="s">
-        <v>109</v>
-      </c>
-      <c r="K34" s="103" t="s">
-        <v>116</v>
-      </c>
-      <c r="L34" s="103" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="8"/>
-      <c r="B35" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C35" s="76"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H35" s="62"/>
-      <c r="J35" s="73"/>
-      <c r="K35" s="103" t="s">
-        <v>117</v>
-      </c>
-      <c r="L35" s="103" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="8">
+      <c r="G33" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H33" s="57"/>
+    </row>
+    <row r="34" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A34" s="7"/>
+      <c r="B34" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="71" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="D34" s="74">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E34" s="14"/>
+      <c r="F34" s="107">
+        <f>D25</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H34" s="57"/>
+    </row>
+    <row r="35" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A35" s="7"/>
+      <c r="B35" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H35" s="57"/>
+    </row>
+    <row r="36" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A36" s="7">
         <v>3</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15">
+      <c r="C36" s="17"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14">
         <v>2</v>
       </c>
-      <c r="G36" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H36" s="62"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="105" t="s">
-        <v>122</v>
-      </c>
-      <c r="L36" s="105" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A37" s="8">
+      <c r="G36" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H36" s="57"/>
+    </row>
+    <row r="37" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A37" s="7">
         <v>4</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B37" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15">
+      <c r="C37" s="18"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14">
         <v>2</v>
       </c>
-      <c r="G37" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H37" s="62"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="103" t="s">
-        <v>118</v>
-      </c>
-      <c r="L37" s="103" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A38" s="8">
+      <c r="G37" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H37" s="57"/>
+    </row>
+    <row r="38" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A38" s="7">
         <v>5</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15">
+      <c r="C38" s="19"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14">
         <f>H10/10</f>
         <v>30</v>
       </c>
-      <c r="G38" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H38" s="62"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="103" t="s">
-        <v>119</v>
-      </c>
-      <c r="L38" s="103" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A39" s="8">
+      <c r="G38" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H38" s="57"/>
+    </row>
+    <row r="39" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A39" s="7">
         <v>6</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15">
+      <c r="C39" s="19"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14">
         <f>H10</f>
         <v>300</v>
       </c>
-      <c r="G39" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H39" s="62"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A40" s="8">
+      <c r="G39" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H39" s="57"/>
+    </row>
+    <row r="40" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A40" s="7">
         <v>7</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15">
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14">
         <v>2</v>
       </c>
-      <c r="G40" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H40" s="62"/>
-    </row>
-    <row r="41" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A41" s="9">
+      <c r="G40" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H40" s="57"/>
+    </row>
+    <row r="41" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A41" s="8">
         <v>8</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="13"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14">
+        <v>2</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H41" s="57"/>
+    </row>
+    <row r="42" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A42" s="8">
+        <v>9</v>
+      </c>
+      <c r="B42" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15">
+      <c r="C42" s="13"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14">
         <v>2</v>
       </c>
-      <c r="G41" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H41" s="62"/>
-    </row>
-    <row r="42" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A42" s="9">
-        <v>9</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15">
-        <v>2</v>
-      </c>
-      <c r="G42" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="H42" s="62"/>
-    </row>
-    <row r="43" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A43" s="22"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="24"/>
-      <c r="G43" s="24"/>
-      <c r="H43" s="55"/>
-    </row>
-    <row r="44" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A44" s="22"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="55"/>
-    </row>
-    <row r="45" spans="1:12" s="17" customFormat="1" ht="21" customHeight="1">
-      <c r="A45" s="22"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="55"/>
-    </row>
-    <row r="46" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
-      <c r="A46" s="10"/>
-      <c r="B46" s="25"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10" t="s">
+      <c r="G42" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42" s="57"/>
+    </row>
+    <row r="43" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A43" s="21"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="53"/>
+    </row>
+    <row r="44" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A44" s="21"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="53"/>
+    </row>
+    <row r="45" spans="1:8" s="16" customFormat="1" ht="21" customHeight="1">
+      <c r="A45" s="21"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="53"/>
+    </row>
+    <row r="46" spans="1:8" s="10" customFormat="1" ht="21" customHeight="1">
+      <c r="A46" s="9"/>
+      <c r="B46" s="24"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+    </row>
+    <row r="47" spans="1:8" s="10" customFormat="1" ht="21" customHeight="1">
+      <c r="A47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="H47" s="43"/>
+    </row>
+    <row r="48" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1">
+      <c r="A48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="43"/>
+    </row>
+    <row r="49" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1">
+      <c r="A49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="43"/>
+    </row>
+    <row r="50" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1">
+      <c r="A50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="12"/>
-      <c r="H46" s="44"/>
-    </row>
-    <row r="47" spans="1:12" s="11" customFormat="1" ht="21" customHeight="1">
-      <c r="A47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="H47" s="44"/>
-    </row>
-    <row r="48" spans="1:12" s="11" customFormat="1" ht="18" customHeight="1">
-      <c r="A48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="44"/>
-    </row>
-    <row r="49" spans="1:8" s="11" customFormat="1" ht="18" customHeight="1">
-      <c r="A49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="44"/>
-    </row>
-    <row r="50" spans="1:8" s="11" customFormat="1" ht="18" customHeight="1">
-      <c r="A50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G50" s="59"/>
+      <c r="G50" s="56"/>
       <c r="H50" s="56"/>
     </row>
-    <row r="51" spans="1:8" s="11" customFormat="1" ht="18" customHeight="1">
-      <c r="A51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="44"/>
-    </row>
-    <row r="52" spans="1:8" s="11" customFormat="1" ht="18" customHeight="1">
-      <c r="A52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="44"/>
-    </row>
-    <row r="53" spans="1:8" s="11" customFormat="1" ht="18" customHeight="1">
-      <c r="A53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="44"/>
+    <row r="51" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1">
+      <c r="A51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="43"/>
+    </row>
+    <row r="52" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1">
+      <c r="A52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="43"/>
+    </row>
+    <row r="53" spans="1:8" s="10" customFormat="1" ht="18" customHeight="1">
+      <c r="A53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <sheetProtection algorithmName="SHA-512" hashValue="5VqRrl/GQ10mFEQcHSxsVrEEF9nYUEldJW8fAKG0ijDClIOMmKWygQA3LlWVpRXfD8VDdrrCrhi1H81d1iw/PQ==" saltValue="tMRpxoPt6GqEk4j4MBp+wg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="B41 G26 F23:F27 C22 H8:H12 B8 B11:B12" name="Range2"/>
+  </protectedRanges>
+  <mergeCells count="12">
     <mergeCell ref="H29:H30"/>
-    <mergeCell ref="D12:F12"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="B2:G6"/>
     <mergeCell ref="A29:A30"/>
@@ -3658,22 +3616,45 @@
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="F29:F30"/>
     <mergeCell ref="G29:G30"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F12:G12"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F26" xr:uid="{AA356F1A-0620-4670-A58F-DFDA228FF6D9}">
-      <formula1>"Pharmed, LMT_55,E_3603"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B41" xr:uid="{009A6FE5-DD26-4B76-9373-F3B948CEA9FB}">
+      <formula1>"กาวกวน Cyclohexane, LOCTITE"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.51181102362204722" right="0.31496062992125984" top="0.35433070866141736" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.261811024" right="0" top="0.10433070899999999" bottom="0" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{78BCEDBD-607D-4A0E-BC29-6FA36C2B64EA}">
+          <x14:formula1>
+            <xm:f>'A2'!$D$37:$F$37</xm:f>
+          </x14:formula1>
+          <xm:sqref>F26</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7B084DA1-1168-4D19-B434-CCF3FD04C9C5}">
+          <x14:formula1>
+            <xm:f>_xlfn.XLOOKUP($F$26,'A2'!$D$37:$F$37,'A2'!$D$38:$F$48)</xm:f>
+          </x14:formula1>
+          <xm:sqref>G26</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB66332C-E13E-40F9-9BC4-83CED49F9C2B}">
-  <dimension ref="A1:M48"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="11.4"/>
   <cols>
     <col min="1" max="2" width="14.88671875" style="1" customWidth="1"/>
@@ -3682,7 +3663,7 @@
     <col min="7" max="7" width="11.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="13.6640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" style="87" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" style="81" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.88671875" style="2" customWidth="1"/>
@@ -3691,7 +3672,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="25.95" customHeight="1">
       <c r="A1" s="111" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="B1" s="111"/>
       <c r="C1" s="111"/>
@@ -3702,7 +3683,7 @@
       <c r="H1" s="111"/>
       <c r="I1" s="111"/>
       <c r="J1" s="111"/>
-      <c r="K1" s="63"/>
+      <c r="K1" s="111"/>
     </row>
     <row r="2" spans="1:11" ht="12" customHeight="1">
       <c r="A2" s="111"/>
@@ -3715,6 +3696,7 @@
       <c r="H2" s="111"/>
       <c r="I2" s="111"/>
       <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
     </row>
     <row r="3" spans="1:11" ht="12" customHeight="1">
       <c r="A3" s="111"/>
@@ -3727,6 +3709,7 @@
       <c r="H3" s="111"/>
       <c r="I3" s="111"/>
       <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
     </row>
     <row r="4" spans="1:11" ht="12" customHeight="1">
       <c r="A4" s="111"/>
@@ -3739,6 +3722,7 @@
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
       <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
     </row>
     <row r="5" spans="1:11" ht="12" customHeight="1">
       <c r="A5" s="111"/>
@@ -3751,10 +3735,11 @@
       <c r="H5" s="111"/>
       <c r="I5" s="111"/>
       <c r="J5" s="111"/>
+      <c r="K5" s="111"/>
     </row>
     <row r="6" spans="1:11" ht="55.95" customHeight="1">
       <c r="A6" s="110" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="110"/>
       <c r="C6" s="110"/>
@@ -3767,811 +3752,870 @@
       <c r="J6" s="110"/>
       <c r="K6" s="110"/>
     </row>
-    <row r="7" spans="1:11" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A7" s="26" t="s">
+    <row r="7" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A7" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="27">
+      <c r="B7" s="25"/>
+      <c r="C7" s="26" t="str">
         <f>'A1'!B8</f>
-        <v>46238</v>
-      </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="H7" s="102" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="86" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="88">
+        <v>08-Aug-2026</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="H7" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="82">
         <f>'A1'!H8</f>
         <v>0</v>
       </c>
-      <c r="K7" s="27"/>
-    </row>
-    <row r="8" spans="1:11" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A8" s="26" t="s">
+      <c r="K7" s="26"/>
+    </row>
+    <row r="8" spans="1:11" s="27" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A8" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="28" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="I8" s="10" t="s">
+      <c r="G8" s="25"/>
+      <c r="H8" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="83">
         <f>'A1'!H9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A9" s="26" t="s">
+        <v>123450</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" s="27" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A9" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="102" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="27"/>
-      <c r="J9" s="86">
+      <c r="B9" s="25"/>
+      <c r="C9" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="25"/>
+      <c r="H9" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="26"/>
+      <c r="J9" s="80" t="str">
         <f>'A1'!H11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="28" customFormat="1" ht="193.2" customHeight="1">
-      <c r="A10" s="26"/>
-      <c r="B10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="J10" s="86"/>
-    </row>
-    <row r="11" spans="1:11" s="28" customFormat="1" ht="28.95" customHeight="1">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="98">
+        <v>002/20260820</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="27" customFormat="1" ht="193.2" customHeight="1">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="J10" s="80"/>
+    </row>
+    <row r="11" spans="1:11" s="27" customFormat="1" ht="28.95" customHeight="1">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="91">
         <f>'A1'!G19</f>
         <v>368.3</v>
       </c>
-      <c r="H11" s="98">
+      <c r="H11" s="91">
         <f>'A1'!H19</f>
         <v>393.7</v>
       </c>
-      <c r="I11" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="86"/>
-    </row>
-    <row r="12" spans="1:11" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="99">
+      <c r="I11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="80"/>
+    </row>
+    <row r="12" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A12" s="25"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="92">
         <f>'A1'!G20</f>
         <v>107.95</v>
       </c>
-      <c r="H12" s="98">
+      <c r="H12" s="91">
         <f>'A1'!H20</f>
         <v>120.64999999999999</v>
       </c>
-      <c r="I12" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J12" s="86"/>
-    </row>
-    <row r="13" spans="1:11" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="28" t="s">
+      <c r="I12" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="99">
+      <c r="J12" s="80"/>
+    </row>
+    <row r="13" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="92">
         <f>'A1'!G21</f>
         <v>150.36999999999998</v>
       </c>
-      <c r="H13" s="98">
+      <c r="H13" s="91">
         <f>'A1'!H21</f>
         <v>153.41</v>
       </c>
-      <c r="I13" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="86"/>
-    </row>
-    <row r="14" spans="1:11" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="28">
+      <c r="I13" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="80"/>
+    </row>
+    <row r="14" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="27">
         <f>'A1'!C22</f>
+        <v>3</v>
+      </c>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="J14" s="80"/>
+    </row>
+    <row r="15" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" s="80" t="str">
+        <f>'A1'!F23</f>
+        <v>เหลือง</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="J15" s="80"/>
+    </row>
+    <row r="16" spans="1:11" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="C16" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="80" t="str">
+        <f>'A1'!F24</f>
+        <v>เขียว</v>
+      </c>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="J16" s="80"/>
+    </row>
+    <row r="17" spans="1:10" s="5" customFormat="1" ht="21" customHeight="1">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="84" t="str">
+        <f>'A1'!F25</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="F17" s="28"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="J17" s="84"/>
+    </row>
+    <row r="18" spans="1:10" s="27" customFormat="1" ht="34.200000000000003" customHeight="1">
+      <c r="A18" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="41"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="J18" s="80"/>
+    </row>
+    <row r="19" spans="1:10" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="J19" s="80"/>
+    </row>
+    <row r="20" spans="1:10" s="27" customFormat="1" ht="30.45" customHeight="1">
+      <c r="A20" s="141" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="127" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="128"/>
+      <c r="D20" s="128"/>
+      <c r="E20" s="129"/>
+      <c r="F20" s="109" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="134"/>
+      <c r="I20" s="137" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="138"/>
+    </row>
+    <row r="21" spans="1:10" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A21" s="141"/>
+      <c r="B21" s="130"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="109"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="136"/>
+      <c r="I21" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="85" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A22" s="29">
+        <v>1</v>
+      </c>
+      <c r="B22" s="121" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="122"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="139" t="s">
+        <v>12</v>
+      </c>
+      <c r="H22" s="140"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="86"/>
+    </row>
+    <row r="23" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A23" s="31">
         <v>2</v>
       </c>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="J14" s="86"/>
-    </row>
-    <row r="15" spans="1:11" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="28" t="s">
+      <c r="B23" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="J15" s="86"/>
-    </row>
-    <row r="16" spans="1:11" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="J16" s="86"/>
-    </row>
-    <row r="17" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="J17" s="90"/>
-    </row>
-    <row r="18" spans="1:10" s="28" customFormat="1" ht="34.200000000000003" customHeight="1">
-      <c r="A18" s="42" t="s">
+      <c r="H23" s="140"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="87"/>
+    </row>
+    <row r="24" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A24" s="31">
+        <v>3</v>
+      </c>
+      <c r="B24" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="139" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="140"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="87"/>
+    </row>
+    <row r="25" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A25" s="31">
+        <v>4</v>
+      </c>
+      <c r="B25" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="42"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="J18" s="86"/>
-    </row>
-    <row r="19" spans="1:10" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="J19" s="86"/>
-    </row>
-    <row r="20" spans="1:10" s="28" customFormat="1" ht="30.45" customHeight="1">
-      <c r="A20" s="125" t="s">
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="139" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="140"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="87"/>
+    </row>
+    <row r="26" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A26" s="31">
         <v>5</v>
       </c>
-      <c r="B20" s="129" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="130"/>
-      <c r="D20" s="130"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="108" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="135" t="s">
-        <v>46</v>
-      </c>
-      <c r="H20" s="136"/>
-      <c r="I20" s="139" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="140"/>
-    </row>
-    <row r="21" spans="1:10" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A21" s="125"/>
-      <c r="B21" s="132"/>
-      <c r="C21" s="133"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="134"/>
-      <c r="F21" s="108"/>
-      <c r="G21" s="137"/>
-      <c r="H21" s="138"/>
-      <c r="I21" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="J21" s="91" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A22" s="30">
-        <v>1</v>
-      </c>
-      <c r="B22" s="122" t="s">
-        <v>19</v>
-      </c>
-      <c r="C22" s="123"/>
-      <c r="D22" s="123"/>
-      <c r="E22" s="124"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="120" t="s">
+      <c r="B26" s="121" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="122"/>
+      <c r="D26" s="122"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="H22" s="121"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="92"/>
-    </row>
-    <row r="23" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A23" s="32">
-        <v>2</v>
-      </c>
-      <c r="B23" s="122" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="123"/>
-      <c r="D23" s="123"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="120" t="s">
+      <c r="H26" s="140"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="87"/>
+    </row>
+    <row r="27" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A27" s="31">
+        <v>6</v>
+      </c>
+      <c r="B27" s="121" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="H23" s="121"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="93"/>
-    </row>
-    <row r="24" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A24" s="32">
-        <v>3</v>
-      </c>
-      <c r="B24" s="122" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="123"/>
-      <c r="D24" s="123"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="120" t="s">
+      <c r="H27" s="140"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="87"/>
+    </row>
+    <row r="28" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A28" s="31">
+        <v>7</v>
+      </c>
+      <c r="B28" s="121" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="122"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="121"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="93"/>
-    </row>
-    <row r="25" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A25" s="32">
-        <v>4</v>
-      </c>
-      <c r="B25" s="122" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="123"/>
-      <c r="D25" s="123"/>
-      <c r="E25" s="124"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="120" t="s">
+      <c r="H28" s="140"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="87"/>
+    </row>
+    <row r="29" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A29" s="36">
+        <v>8</v>
+      </c>
+      <c r="B29" s="121" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="122"/>
+      <c r="D29" s="122"/>
+      <c r="E29" s="123"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="H25" s="121"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="93"/>
-    </row>
-    <row r="26" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A26" s="32">
-        <v>5</v>
-      </c>
-      <c r="B26" s="122" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="123"/>
-      <c r="D26" s="123"/>
-      <c r="E26" s="124"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="120" t="s">
+      <c r="H29" s="140"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="87"/>
+    </row>
+    <row r="30" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A30" s="36">
+        <v>9</v>
+      </c>
+      <c r="B30" s="121" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="122"/>
+      <c r="D30" s="122"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="H26" s="121"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="93"/>
-    </row>
-    <row r="27" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A27" s="32">
-        <v>6</v>
-      </c>
-      <c r="B27" s="122" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="123"/>
-      <c r="D27" s="123"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="120" t="s">
+      <c r="H30" s="140"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="87"/>
+    </row>
+    <row r="31" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A31" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="H27" s="121"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="93"/>
-    </row>
-    <row r="28" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A28" s="32">
-        <v>7</v>
-      </c>
-      <c r="B28" s="122" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="123"/>
-      <c r="D28" s="123"/>
-      <c r="E28" s="124"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="120" t="s">
+      <c r="B31" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="H28" s="121"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="93"/>
-    </row>
-    <row r="29" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A29" s="37">
-        <v>8</v>
-      </c>
-      <c r="B29" s="122" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="123"/>
-      <c r="D29" s="123"/>
-      <c r="E29" s="124"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="120" t="s">
+      <c r="C31" s="125"/>
+      <c r="D31" s="125"/>
+      <c r="E31" s="126"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="121"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="93"/>
-    </row>
-    <row r="30" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A30" s="37">
-        <v>9</v>
-      </c>
-      <c r="B30" s="122" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="123"/>
-      <c r="D30" s="123"/>
-      <c r="E30" s="124"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="120" t="s">
+      <c r="H31" s="140"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="87"/>
+    </row>
+    <row r="32" spans="1:10" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A32" s="37"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="H30" s="121"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="93"/>
-    </row>
-    <row r="31" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A31" s="37" t="s">
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="39"/>
+      <c r="J32" s="88"/>
+    </row>
+    <row r="33" spans="1:13" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A33" s="37"/>
+      <c r="B33" s="37"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="39"/>
+      <c r="J33" s="88"/>
+    </row>
+    <row r="34" spans="1:13" s="33" customFormat="1" ht="21" customHeight="1">
+      <c r="A34" s="37"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="39"/>
+      <c r="J34" s="88"/>
+    </row>
+    <row r="35" spans="1:13" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A35" s="25"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="126" t="s">
+      <c r="I35" s="26"/>
+      <c r="J35" s="80"/>
+    </row>
+    <row r="36" spans="1:13" s="27" customFormat="1" ht="21" customHeight="1">
+      <c r="A36" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="142"/>
+      <c r="C36" s="142"/>
+      <c r="D36" s="142"/>
+      <c r="E36" s="142"/>
+      <c r="F36" s="142"/>
+      <c r="G36" s="142"/>
+      <c r="H36" s="142"/>
+      <c r="I36" s="142"/>
+      <c r="J36" s="142"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="142"/>
+      <c r="M36" s="142"/>
+    </row>
+    <row r="37" spans="1:13" s="27" customFormat="1" ht="40.950000000000003" customHeight="1">
+      <c r="A37" s="66" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="66" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="E37" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="F37" s="66" t="s">
+        <v>103</v>
+      </c>
+      <c r="G37" s="66" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="I37" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="J37" s="89" t="s">
+        <v>69</v>
+      </c>
+      <c r="K37" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="L37" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="M37" s="66" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="27" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A38" s="67" t="s">
+        <v>72</v>
+      </c>
+      <c r="B38" s="67">
+        <v>1.02</v>
+      </c>
+      <c r="C38" s="67">
+        <v>2.72</v>
+      </c>
+      <c r="D38" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" s="94" t="s">
+        <v>117</v>
+      </c>
+      <c r="G38" s="67">
+        <v>152</v>
+      </c>
+      <c r="H38" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="J38" s="90"/>
+      <c r="K38" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="M38" s="67"/>
+    </row>
+    <row r="39" spans="1:13" s="27" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A39" s="67" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="67">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="C39" s="67">
+        <v>2.79</v>
+      </c>
+      <c r="D39" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="E39" s="94" t="s">
+        <v>110</v>
+      </c>
+      <c r="F39" s="94" t="s">
+        <v>118</v>
+      </c>
+      <c r="G39" s="67">
+        <v>152</v>
+      </c>
+      <c r="H39" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="67" t="s">
+        <v>87</v>
+      </c>
+      <c r="J39" s="90"/>
+      <c r="K39" s="67" t="s">
+        <v>74</v>
+      </c>
+      <c r="L39" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="M39" s="67"/>
+    </row>
+    <row r="40" spans="1:13" s="27" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A40" s="67" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="67">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="C40" s="67">
+        <v>2.84</v>
+      </c>
+      <c r="D40" s="67" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="F40" s="95" t="s">
+        <v>119</v>
+      </c>
+      <c r="G40" s="67">
+        <v>152</v>
+      </c>
+      <c r="H40" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="I40" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="J40" s="90"/>
+      <c r="K40" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="M40" s="67"/>
+    </row>
+    <row r="41" spans="1:13" s="27" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A41" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" s="67">
+        <v>1.22</v>
+      </c>
+      <c r="C41" s="67">
+        <v>2.92</v>
+      </c>
+      <c r="D41" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="E41" s="94" t="s">
+        <v>111</v>
+      </c>
+      <c r="F41" s="94" t="s">
+        <v>120</v>
+      </c>
+      <c r="G41" s="67">
+        <v>152</v>
+      </c>
+      <c r="H41" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="I41" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="J41" s="90"/>
+      <c r="K41" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="L41" s="67" t="s">
+        <v>90</v>
+      </c>
+      <c r="M41" s="67"/>
+    </row>
+    <row r="42" spans="1:13" s="27" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A42" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" s="67">
+        <v>1.65</v>
+      </c>
+      <c r="C42" s="67">
+        <v>3.35</v>
+      </c>
+      <c r="D42" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="F42" s="94" t="s">
+        <v>121</v>
+      </c>
+      <c r="G42" s="67">
+        <v>152</v>
+      </c>
+      <c r="H42" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="J42" s="90"/>
+      <c r="K42" s="67" t="s">
+        <v>79</v>
+      </c>
+      <c r="L42" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="M42" s="67"/>
+    </row>
+    <row r="43" spans="1:13" s="27" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A43" s="67" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" s="67">
+        <v>1.75</v>
+      </c>
+      <c r="C43" s="67">
+        <v>3.45</v>
+      </c>
+      <c r="D43" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="E43" s="95" t="s">
+        <v>116</v>
+      </c>
+      <c r="F43" s="96" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43" s="67">
+        <v>152</v>
+      </c>
+      <c r="H43" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="J43" s="90"/>
+      <c r="K43" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="L43" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="M43" s="67"/>
+    </row>
+    <row r="44" spans="1:13" s="27" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A44" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="67">
+        <v>1.85</v>
+      </c>
+      <c r="C44" s="67">
+        <v>3.55</v>
+      </c>
+      <c r="D44" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="E44" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="F44" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="G44" s="67">
+        <v>152</v>
+      </c>
+      <c r="H44" s="67" t="s">
+        <v>27</v>
+      </c>
+      <c r="I44" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="J44" s="90"/>
+      <c r="K44" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="L44" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="M44" s="67"/>
+    </row>
+    <row r="45" spans="1:13" s="3" customFormat="1" ht="25.2" customHeight="1">
+      <c r="A45" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" s="67">
+        <v>2.06</v>
+      </c>
+      <c r="C45" s="67">
+        <v>3.76</v>
+      </c>
+      <c r="D45" s="67"/>
+      <c r="E45" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="F45" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="G45" s="67">
+        <v>152</v>
+      </c>
+      <c r="H45" s="68" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="J45" s="90"/>
+      <c r="K45" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="L45" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="M45" s="67"/>
+    </row>
+    <row r="46" spans="1:13" s="105" customFormat="1" ht="19.2" customHeight="1">
+      <c r="A46" s="108" t="s">
+        <v>132</v>
+      </c>
+      <c r="B46" s="108">
+        <v>0.44</v>
+      </c>
+      <c r="C46" s="108">
+        <v>0.89</v>
+      </c>
+      <c r="D46" s="108"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108" t="s">
+        <v>133</v>
+      </c>
+      <c r="G46" s="108">
+        <v>381</v>
+      </c>
+      <c r="H46" s="108" t="s">
+        <v>135</v>
+      </c>
+      <c r="I46" s="108" t="s">
+        <v>88</v>
+      </c>
+      <c r="J46" s="108"/>
+      <c r="K46" s="108" t="s">
+        <v>136</v>
+      </c>
+      <c r="L46" s="108" t="s">
+        <v>134</v>
+      </c>
+      <c r="M46" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="127"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="128"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="120" t="s">
-        <v>12</v>
-      </c>
-      <c r="H31" s="121"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="93"/>
-    </row>
-    <row r="32" spans="1:10" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A32" s="38"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="40"/>
-      <c r="J32" s="94"/>
-    </row>
-    <row r="33" spans="1:13" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A33" s="38"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="40"/>
-      <c r="J33" s="94"/>
-    </row>
-    <row r="34" spans="1:13" s="34" customFormat="1" ht="21" customHeight="1">
-      <c r="A34" s="38"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="40"/>
-      <c r="J34" s="94"/>
-    </row>
-    <row r="35" spans="1:13" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A35" s="26"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I35" s="27"/>
-      <c r="J35" s="86"/>
-    </row>
-    <row r="36" spans="1:13" s="28" customFormat="1" ht="21" customHeight="1">
-      <c r="A36" s="119" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="119"/>
-      <c r="C36" s="119"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="119"/>
-      <c r="H36" s="119"/>
-      <c r="I36" s="119"/>
-      <c r="J36" s="119"/>
-      <c r="K36" s="119"/>
-      <c r="L36" s="119"/>
-      <c r="M36" s="119"/>
-    </row>
-    <row r="37" spans="1:13" s="28" customFormat="1" ht="40.950000000000003" customHeight="1">
-      <c r="A37" s="72" t="s">
-        <v>65</v>
-      </c>
-      <c r="B37" s="72" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="72" t="s">
-        <v>67</v>
-      </c>
-      <c r="D37" s="72" t="s">
-        <v>104</v>
-      </c>
-      <c r="E37" s="72" t="s">
-        <v>105</v>
-      </c>
-      <c r="F37" s="72" t="s">
-        <v>106</v>
-      </c>
-      <c r="G37" s="72" t="s">
-        <v>68</v>
-      </c>
-      <c r="H37" s="72" t="s">
-        <v>69</v>
-      </c>
-      <c r="I37" s="72" t="s">
-        <v>70</v>
-      </c>
-      <c r="J37" s="95" t="s">
-        <v>71</v>
-      </c>
-      <c r="K37" s="72" t="s">
-        <v>72</v>
-      </c>
-      <c r="L37" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="M37" s="72" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" s="28" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A38" s="73" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="73">
-        <v>1.02</v>
-      </c>
-      <c r="C38" s="73">
-        <v>2.72</v>
-      </c>
-      <c r="D38" s="73" t="s">
-        <v>128</v>
-      </c>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="73">
-        <v>152</v>
-      </c>
-      <c r="H38" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="I38" s="73" t="s">
-        <v>89</v>
-      </c>
-      <c r="J38" s="96"/>
-      <c r="K38" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="L38" s="73" t="s">
-        <v>89</v>
-      </c>
-      <c r="M38" s="73"/>
-    </row>
-    <row r="39" spans="1:13" s="28" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A39" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" s="73">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="C39" s="73">
-        <v>2.79</v>
-      </c>
-      <c r="D39" s="73"/>
-      <c r="E39" s="103"/>
-      <c r="F39" s="103"/>
-      <c r="G39" s="73">
-        <v>152</v>
-      </c>
-      <c r="H39" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="I39" s="73" t="s">
-        <v>89</v>
-      </c>
-      <c r="J39" s="96"/>
-      <c r="K39" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="L39" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="M39" s="73"/>
-    </row>
-    <row r="40" spans="1:13" s="28" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A40" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B40" s="73">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="C40" s="73">
-        <v>2.84</v>
-      </c>
-      <c r="D40" s="73" t="s">
-        <v>125</v>
-      </c>
-      <c r="E40" s="103"/>
-      <c r="F40" s="104"/>
-      <c r="G40" s="73">
-        <v>152</v>
-      </c>
-      <c r="H40" s="73" t="s">
-        <v>26</v>
-      </c>
-      <c r="I40" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="J40" s="96"/>
-      <c r="K40" s="73" t="s">
-        <v>26</v>
-      </c>
-      <c r="L40" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="M40" s="73"/>
-    </row>
-    <row r="41" spans="1:13" s="28" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A41" s="73" t="s">
-        <v>78</v>
-      </c>
-      <c r="B41" s="73">
-        <v>1.22</v>
-      </c>
-      <c r="C41" s="73">
-        <v>2.92</v>
-      </c>
-      <c r="D41" s="73"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="73">
-        <v>152</v>
-      </c>
-      <c r="H41" s="73" t="s">
-        <v>26</v>
-      </c>
-      <c r="I41" s="73" t="s">
-        <v>91</v>
-      </c>
-      <c r="J41" s="96"/>
-      <c r="K41" s="73" t="s">
-        <v>79</v>
-      </c>
-      <c r="L41" s="73" t="s">
-        <v>92</v>
-      </c>
-      <c r="M41" s="73"/>
-    </row>
-    <row r="42" spans="1:13" s="28" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A42" s="73" t="s">
-        <v>80</v>
-      </c>
-      <c r="B42" s="73">
-        <v>1.65</v>
-      </c>
-      <c r="C42" s="73">
-        <v>3.35</v>
-      </c>
-      <c r="D42" s="73"/>
-      <c r="E42" s="103"/>
-      <c r="F42" s="103"/>
-      <c r="G42" s="73">
-        <v>152</v>
-      </c>
-      <c r="H42" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="J42" s="96"/>
-      <c r="K42" s="73" t="s">
-        <v>81</v>
-      </c>
-      <c r="L42" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="M42" s="73"/>
-    </row>
-    <row r="43" spans="1:13" s="28" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A43" s="73" t="s">
-        <v>82</v>
-      </c>
-      <c r="B43" s="73">
-        <v>1.75</v>
-      </c>
-      <c r="C43" s="73">
-        <v>3.45</v>
-      </c>
-      <c r="D43" s="73"/>
-      <c r="E43" s="104" t="s">
-        <v>121</v>
-      </c>
-      <c r="F43" s="105"/>
-      <c r="G43" s="73">
-        <v>152</v>
-      </c>
-      <c r="H43" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="I43" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="J43" s="96"/>
-      <c r="K43" s="73" t="s">
-        <v>83</v>
-      </c>
-      <c r="L43" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="M43" s="73"/>
-    </row>
-    <row r="44" spans="1:13" s="28" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A44" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="73">
-        <v>1.85</v>
-      </c>
-      <c r="C44" s="73">
-        <v>3.55</v>
-      </c>
-      <c r="D44" s="73"/>
-      <c r="E44" s="103"/>
-      <c r="F44" s="103" t="s">
-        <v>128</v>
-      </c>
-      <c r="G44" s="73">
-        <v>152</v>
-      </c>
-      <c r="H44" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="J44" s="96"/>
-      <c r="K44" s="73" t="s">
-        <v>83</v>
-      </c>
-      <c r="L44" s="73" t="s">
-        <v>90</v>
-      </c>
-      <c r="M44" s="73"/>
-    </row>
-    <row r="45" spans="1:13" s="4" customFormat="1" ht="25.2" customHeight="1">
-      <c r="A45" s="73" t="s">
-        <v>85</v>
-      </c>
-      <c r="B45" s="73">
-        <v>2.06</v>
-      </c>
-      <c r="C45" s="73">
-        <v>3.76</v>
-      </c>
-      <c r="D45" s="73"/>
-      <c r="E45" s="103"/>
-      <c r="F45" s="103"/>
-      <c r="G45" s="73">
-        <v>152</v>
-      </c>
-      <c r="H45" s="74" t="s">
-        <v>29</v>
-      </c>
-      <c r="I45" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="J45" s="96"/>
-      <c r="K45" s="73" t="s">
-        <v>29</v>
-      </c>
-      <c r="L45" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="M45" s="73"/>
-    </row>
-    <row r="46" spans="1:13" s="4" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="J46" s="97"/>
-    </row>
-    <row r="47" spans="1:13" ht="25.5" customHeight="1">
-      <c r="E47" s="103"/>
-      <c r="F47" s="103"/>
-    </row>
-    <row r="48" spans="1:13" ht="25.5" customHeight="1">
-      <c r="E48" s="103"/>
-      <c r="F48" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B20:E21"/>
-    <mergeCell ref="G20:H21"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A6:K6"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A1:J5"/>
-    <mergeCell ref="B22:E22"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="H36:M36"/>
     <mergeCell ref="G30:H30"/>
@@ -4588,22 +4632,23 @@
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B29:E29"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="A1:K5"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B20:E21"/>
+    <mergeCell ref="G20:H21"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="B23:E23"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
-  <pageMargins left="0.51181102362204722" right="0.11811023622047245" top="0.35433070866141736" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.511811023622047" right="0.118110236220472" top="0.35433070866141703" bottom="0.15748031496063" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FF915FA9-662F-4BBC-ACDC-22805800E086}">
-          <x14:formula1>
-            <xm:f>INDIRECT('A1'!$F$26)</xm:f>
-          </x14:formula1>
-          <xm:sqref>D38:F45</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>